--- a/Utms-Generator/clients/CIC.xlsx
+++ b/Utms-Generator/clients/CIC.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approved UTMs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Approved UTMs'!$A$1:$I$756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Approved UTMs'!$A$1:$I$757</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ApprovedUTMs" displayName="ApprovedUTMs" ref="A1:I756" headerRowCount="1">
-  <autoFilter ref="A1:I756"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ApprovedUTMs" displayName="ApprovedUTMs" ref="A1:I757" headerRowCount="1">
+  <autoFilter ref="A1:I757"/>
   <tableColumns count="9">
     <tableColumn id="1" name="client"/>
     <tableColumn id="2" name="destination_url"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I756"/>
+  <dimension ref="A1:I757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32129,8 +32129,55 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>CIC</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://www.castleintheclouds.org/christmas-at-the-castle/</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>ConstantContact</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>ProgramsAndEvents</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>ChristmasAtTheCastle</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>Purchase</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3UQOcp0</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I756"/>
+  <autoFilter ref="A1:I757"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
